--- a/web/files/港岛-半山区东部-Central Peak II.xlsx
+++ b/web/files/港岛-半山区东部-Central Peak II.xlsx
@@ -17,10 +17,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="$#,##0"/>
-  </numFmts>
-  <fonts count="17">
+  <numFmts count="0"/>
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -106,11 +104,6 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00004D00"/>
       <sz val="8"/>
@@ -192,7 +185,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -204,9 +197,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -242,13 +232,10 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -616,7 +603,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -625,8 +612,8 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
@@ -857,7 +844,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Altus Link 洋房3</t>
+          <t>Bliss Link 洋房3</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -876,11 +863,11 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>3686</v>
+        <v>3688</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -890,12 +877,12 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -905,12 +892,12 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
@@ -920,14 +907,14 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Altus Link 洋房5</t>
+          <t>Bliss Link 洋房6</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -946,7 +933,7 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>4022</v>
+        <v>3691</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -997,7 +984,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Altus Link 洋房6</t>
+          <t>Bliss Link 洋房7</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1016,23 +1003,27 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>4016</v>
+        <v>3686</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>409632000</v>
-      </c>
-      <c r="I7" s="5" t="n">
-        <v>102000</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -1063,7 +1054,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Altus Link 洋房7</t>
+          <t>Bliss Link 洋房8</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1082,7 +1073,7 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>3671</v>
+        <v>3714</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -1133,7 +1124,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Altus Link 洋房8</t>
+          <t>Colmo Link 洋房1</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -1148,11 +1139,11 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>3954</v>
+        <v>2776</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -1203,7 +1194,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Bliss Link 洋房1</t>
+          <t>Colmo Link 洋房2</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1218,27 +1209,31 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>3723</v>
+        <v>2754</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2022-01-09</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="n">
-        <v>386800000</v>
-      </c>
-      <c r="I10" s="5" t="n">
-        <v>103895</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -1269,7 +1264,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Bliss Link 洋房2</t>
+          <t>Colmo Link 洋房3</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -1284,27 +1279,31 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>3695</v>
+        <v>2754</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2021-11-14</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="n">
-        <v>352500000</v>
-      </c>
-      <c r="I11" s="5" t="n">
-        <v>95399</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -1335,7 +1334,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Bliss Link 洋房3</t>
+          <t>Colmo Link 洋房6</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1350,15 +1349,15 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>3688</v>
+        <v>2754</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -1368,12 +1367,12 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1383,12 +1382,12 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -1398,14 +1397,14 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Bliss Link 洋房6</t>
+          <t>Colmo Link 洋房7</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -1420,11 +1419,11 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>3691</v>
+        <v>2754</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -1475,7 +1474,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Bliss Link 洋房7</t>
+          <t>Colmo Link 洋房8</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1490,11 +1489,11 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>3686</v>
+        <v>2780</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -1537,496 +1536,6 @@
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Bliss Link 洋房8</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>3714</v>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M15" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Colmo Link 洋房1</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>2776</v>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M16" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N16" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Colmo Link 洋房2</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>2754</v>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M17" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N17" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>Colmo Link 洋房3</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>2754</v>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M18" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N18" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>Colmo Link 洋房6</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>2754</v>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L19" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M19" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N19" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>Colmo Link 洋房7</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>2754</v>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M20" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N20" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>Colmo Link 洋房8</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>2780</v>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M21" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N21" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -2047,7 +1556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2057,7 +1566,6 @@
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -2068,66 +1576,66 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="9" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>19 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>12 套</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>1 套</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="C3" s="12" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>
       </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>3 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>
       </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>15 套</t>
+      <c r="E3" s="14" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>11 套</t>
         </is>
       </c>
     </row>
@@ -2154,20 +1662,15 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>洋房5</t>
+          <t>洋房6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>洋房6</t>
+          <t>洋房7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>洋房7</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>洋房8</t>
         </is>
@@ -2179,7 +1682,7 @@
           <t>Altus Link</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>Altus Link 洋房1
 3929呎 (4+房)
@@ -2188,7 +1691,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>Altus Link 洋房2
 3648呎 (4+房)
@@ -2197,51 +1700,10 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>Altus Link 洋房3
-3686呎 (4+房)
-(待售)
-暂无价格
-暂无呎价</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>Altus Link 洋房5
-4022呎 (4+房)
-(待售)
-暂无价格
-暂无呎价</t>
-        </is>
-      </c>
-      <c r="F6" s="17" t="inlineStr">
-        <is>
-          <t>Altus Link 洋房6
-4016呎 (4+房)
-(23年-04月-26日)
-$4.10亿
-$102,000/呎</t>
-        </is>
-      </c>
-      <c r="G6" s="16" t="inlineStr">
-        <is>
-          <t>Altus Link 洋房7
-3671呎 (4+房)
-(待售)
-暂无价格
-暂无呎价</t>
-        </is>
-      </c>
-      <c r="H6" s="16" t="inlineStr">
-        <is>
-          <t>Altus Link 洋房8
-3954呎 (4+房)
-(待售)
-暂无价格
-暂无呎价</t>
-        </is>
-      </c>
+      <c r="D6" s="16" t="inlineStr"/>
+      <c r="E6" s="16" t="inlineStr"/>
+      <c r="F6" s="16" t="inlineStr"/>
+      <c r="G6" s="16" t="inlineStr"/>
     </row>
     <row r="7" ht="80" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
@@ -2249,25 +1711,9 @@
           <t>Bliss Link</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>Bliss Link 洋房1
-3723呎 (4+房)
-(22年-01月-09日)
-$3.87亿
-$103,895/呎</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>Bliss Link 洋房2
-3695呎 (4+房)
-(21年-11月-14日)
-$3.52亿
-$95,399/呎</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr"/>
+      <c r="C7" s="16" t="inlineStr"/>
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>Bliss Link 洋房3
 3688呎 (4+房)
@@ -2276,8 +1722,7 @@
 -</t>
         </is>
       </c>
-      <c r="E7" s="19" t="inlineStr"/>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="E7" s="15" t="inlineStr">
         <is>
           <t>Bliss Link 洋房6
 3691呎 (4+房)
@@ -2286,7 +1731,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="F7" s="15" t="inlineStr">
         <is>
           <t>Bliss Link 洋房7
 3686呎 (4+房)
@@ -2295,7 +1740,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="H7" s="16" t="inlineStr">
+      <c r="G7" s="15" t="inlineStr">
         <is>
           <t>Bliss Link 洋房8
 3714呎 (4+房)
@@ -2311,7 +1756,7 @@
           <t>Colmo Link</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>Colmo Link 洋房1
 2776呎 (3房)
@@ -2320,7 +1765,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C8" s="15" t="inlineStr">
         <is>
           <t>Colmo Link 洋房2
 2754呎 (3房)
@@ -2329,7 +1774,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D8" s="15" t="inlineStr">
         <is>
           <t>Colmo Link 洋房3
 2754呎 (3房)
@@ -2338,8 +1783,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="E8" s="19" t="inlineStr"/>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="E8" s="15" t="inlineStr">
         <is>
           <t>Colmo Link 洋房6
 2754呎 (3房)
@@ -2348,7 +1792,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="F8" s="15" t="inlineStr">
         <is>
           <t>Colmo Link 洋房7
 2754呎 (3房)
@@ -2357,7 +1801,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="H8" s="16" t="inlineStr">
+      <c r="G8" s="15" t="inlineStr">
         <is>
           <t>Colmo Link 洋房8
 2780呎 (3房)
@@ -2369,7 +1813,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>

--- a/web/files/港岛-半山区东部-Central Peak II.xlsx
+++ b/web/files/港岛-半山区东部-Central Peak II.xlsx
@@ -17,8 +17,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="16">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="$#,##0"/>
+  </numFmts>
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -104,6 +106,11 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00004D00"/>
       <sz val="8"/>
@@ -185,7 +192,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -197,6 +204,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -232,10 +242,13 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -603,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -612,8 +625,8 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
@@ -844,7 +857,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Bliss Link 洋房3</t>
+          <t>Altus Link 洋房3</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -863,11 +876,11 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>3688</v>
+        <v>3686</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -877,12 +890,12 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -892,12 +905,12 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
@@ -907,14 +920,14 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Bliss Link 洋房6</t>
+          <t>Altus Link 洋房5</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -933,7 +946,7 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>3691</v>
+        <v>4022</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -984,7 +997,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Bliss Link 洋房7</t>
+          <t>Altus Link 洋房6</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1003,27 +1016,23 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>3686</v>
+        <v>4016</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2023-04-27</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>409632000</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>102000</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -1054,7 +1063,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Bliss Link 洋房8</t>
+          <t>Altus Link 洋房7</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1073,7 +1082,7 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>3714</v>
+        <v>3671</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -1124,7 +1133,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Colmo Link 洋房1</t>
+          <t>Altus Link 洋房8</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -1139,11 +1148,11 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>2776</v>
+        <v>3954</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -1194,7 +1203,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Colmo Link 洋房2</t>
+          <t>Bliss Link 洋房1</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1209,31 +1218,27 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>2754</v>
+        <v>3723</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2022-01-10</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>386800000</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>103895</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -1264,7 +1269,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Colmo Link 洋房3</t>
+          <t>Bliss Link 洋房2</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -1279,31 +1284,27 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2754</v>
+        <v>3695</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2021-11-15</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>352500000</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>95399</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -1334,7 +1335,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Colmo Link 洋房6</t>
+          <t>Bliss Link 洋房3</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1349,15 +1350,15 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2754</v>
+        <v>3688</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -1367,12 +1368,12 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1382,12 +1383,12 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -1397,14 +1398,14 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Colmo Link 洋房7</t>
+          <t>Bliss Link 洋房6</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -1419,11 +1420,11 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2754</v>
+        <v>3691</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -1474,68 +1475,558 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
+          <t>Bliss Link 洋房7</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>3686</v>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Bliss Link 洋房8</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>3714</v>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Colmo Link 洋房1</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>2776</v>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Colmo Link 洋房2</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>2754</v>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Colmo Link 洋房3</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>2754</v>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Colmo Link 洋房6</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>2754</v>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Colmo Link 洋房7</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>2754</v>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
           <t>Colmo Link 洋房8</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>3房</t>
         </is>
       </c>
-      <c r="E14" s="4" t="n">
+      <c r="E21" s="4" t="n">
         <v>2780</v>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>待售</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -1556,7 +2047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1566,6 +2057,7 @@
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -1576,66 +2068,66 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="D2" s="9" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="9" t="inlineStr">
+      <c r="E2" s="10" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="10" t="inlineStr">
-        <is>
-          <t>12 套</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>19 套</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>1 套</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>
       </c>
-      <c r="D3" s="13" t="inlineStr">
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>3 套</t>
+        </is>
+      </c>
+      <c r="E3" s="15" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>
       </c>
-      <c r="E3" s="14" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="10" t="inlineStr">
-        <is>
-          <t>11 套</t>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>15 套</t>
         </is>
       </c>
     </row>
@@ -1662,15 +2154,20 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>洋房5</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>洋房6</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>洋房7</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>洋房8</t>
         </is>
@@ -1682,7 +2179,7 @@
           <t>Altus Link</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>Altus Link 洋房1
 3929呎 (4+房)
@@ -1691,7 +2188,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>Altus Link 洋房2
 3648呎 (4+房)
@@ -1700,10 +2197,51 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr"/>
-      <c r="E6" s="16" t="inlineStr"/>
-      <c r="F6" s="16" t="inlineStr"/>
-      <c r="G6" s="16" t="inlineStr"/>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>Altus Link 洋房3
+3686呎 (4+房)
+(待售)
+暂无价格
+暂无呎价</t>
+        </is>
+      </c>
+      <c r="E6" s="16" t="inlineStr">
+        <is>
+          <t>Altus Link 洋房5
+4022呎 (4+房)
+(待售)
+暂无价格
+暂无呎价</t>
+        </is>
+      </c>
+      <c r="F6" s="17" t="inlineStr">
+        <is>
+          <t>Altus Link 洋房6
+4016呎 (4+房)
+(23年-04月-27日)
+$4.10亿
+$102,000/呎</t>
+        </is>
+      </c>
+      <c r="G6" s="16" t="inlineStr">
+        <is>
+          <t>Altus Link 洋房7
+3671呎 (4+房)
+(待售)
+暂无价格
+暂无呎价</t>
+        </is>
+      </c>
+      <c r="H6" s="16" t="inlineStr">
+        <is>
+          <t>Altus Link 洋房8
+3954呎 (4+房)
+(待售)
+暂无价格
+暂无呎价</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="80" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
@@ -1711,9 +2249,25 @@
           <t>Bliss Link</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr"/>
-      <c r="C7" s="16" t="inlineStr"/>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>Bliss Link 洋房1
+3723呎 (4+房)
+(22年-01月-10日)
+$3.87亿
+$103,895/呎</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>Bliss Link 洋房2
+3695呎 (4+房)
+(21年-11月-15日)
+$3.52亿
+$95,399/呎</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="inlineStr">
         <is>
           <t>Bliss Link 洋房3
 3688呎 (4+房)
@@ -1722,7 +2276,8 @@
 -</t>
         </is>
       </c>
-      <c r="E7" s="15" t="inlineStr">
+      <c r="E7" s="19" t="inlineStr"/>
+      <c r="F7" s="16" t="inlineStr">
         <is>
           <t>Bliss Link 洋房6
 3691呎 (4+房)
@@ -1731,7 +2286,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="F7" s="15" t="inlineStr">
+      <c r="G7" s="16" t="inlineStr">
         <is>
           <t>Bliss Link 洋房7
 3686呎 (4+房)
@@ -1740,7 +2295,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="G7" s="15" t="inlineStr">
+      <c r="H7" s="16" t="inlineStr">
         <is>
           <t>Bliss Link 洋房8
 3714呎 (4+房)
@@ -1756,7 +2311,7 @@
           <t>Colmo Link</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>Colmo Link 洋房1
 2776呎 (3房)
@@ -1765,7 +2320,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>Colmo Link 洋房2
 2754呎 (3房)
@@ -1774,7 +2329,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="D8" s="15" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>Colmo Link 洋房3
 2754呎 (3房)
@@ -1783,7 +2338,8 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="E8" s="15" t="inlineStr">
+      <c r="E8" s="19" t="inlineStr"/>
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>Colmo Link 洋房6
 2754呎 (3房)
@@ -1792,7 +2348,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="F8" s="15" t="inlineStr">
+      <c r="G8" s="16" t="inlineStr">
         <is>
           <t>Colmo Link 洋房7
 2754呎 (3房)
@@ -1801,7 +2357,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="G8" s="15" t="inlineStr">
+      <c r="H8" s="16" t="inlineStr">
         <is>
           <t>Colmo Link 洋房8
 2780呎 (3房)
@@ -1813,7 +2369,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>

--- a/web/files/港岛-半山区东部-Central Peak II.xlsx
+++ b/web/files/港岛-半山区东部-Central Peak II.xlsx
@@ -242,13 +242,13 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -997,7 +997,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Altus Link 洋房6</t>
+          <t>Altus Link 洋房7</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1016,23 +1016,27 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>4016</v>
+        <v>3671</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2023-04-27</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>409632000</v>
-      </c>
-      <c r="I7" s="5" t="n">
-        <v>102000</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -1063,7 +1067,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Altus Link 洋房7</t>
+          <t>Altus Link 洋房8</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1082,7 +1086,7 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>3671</v>
+        <v>3954</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -1133,7 +1137,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Altus Link 洋房8</t>
+          <t>Bliss Link 洋房1</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -1152,27 +1156,23 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>3954</v>
+        <v>3723</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2022-01-10</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>386800000</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>103895</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Bliss Link 洋房1</t>
+          <t>Bliss Link 洋房3</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1222,23 +1222,27 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>3723</v>
+        <v>3688</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2022-01-10</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="n">
-        <v>386800000</v>
-      </c>
-      <c r="I10" s="5" t="n">
-        <v>103895</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -1247,12 +1251,12 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -1262,14 +1266,14 @@
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Bliss Link 洋房2</t>
+          <t>Bliss Link 洋房6</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -1288,23 +1292,27 @@
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>3695</v>
+        <v>3691</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2021-11-15</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="n">
-        <v>352500000</v>
-      </c>
-      <c r="I11" s="5" t="n">
-        <v>95399</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -1335,7 +1343,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Bliss Link 洋房3</t>
+          <t>Bliss Link 洋房7</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1354,11 +1362,11 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>3688</v>
+        <v>3686</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -1368,12 +1376,12 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1383,12 +1391,12 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -1398,14 +1406,14 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Bliss Link 洋房6</t>
+          <t>Colmo Link 洋房1</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -1420,11 +1428,11 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>3691</v>
+        <v>2776</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -1475,7 +1483,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Bliss Link 洋房7</t>
+          <t>Colmo Link 洋房2</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1490,11 +1498,11 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>3686</v>
+        <v>2754</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -1545,7 +1553,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Bliss Link 洋房8</t>
+          <t>Colmo Link 洋房3</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -1560,11 +1568,11 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>3714</v>
+        <v>2754</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -1615,7 +1623,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Colmo Link 洋房1</t>
+          <t>Colmo Link 洋房6</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1634,7 +1642,7 @@
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>2776</v>
+        <v>2754</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -1685,7 +1693,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Colmo Link 洋房2</t>
+          <t>Colmo Link 洋房7</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -1755,7 +1763,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Colmo Link 洋房3</t>
+          <t>Colmo Link 洋房8</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -1774,7 +1782,7 @@
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>2754</v>
+        <v>2780</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -1817,216 +1825,6 @@
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>Colmo Link 洋房6</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>2754</v>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L19" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M19" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N19" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>Colmo Link 洋房7</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>2754</v>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M20" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N20" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>Colmo Link 洋房8</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>2780</v>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M21" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N21" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -2102,7 +1900,7 @@
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>19 套</t>
+          <t>16 套</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
@@ -2117,7 +1915,7 @@
       </c>
       <c r="D3" s="14" t="inlineStr">
         <is>
-          <t>3 套</t>
+          <t>1 套</t>
         </is>
       </c>
       <c r="E3" s="15" t="inlineStr">
@@ -2127,7 +1925,7 @@
       </c>
       <c r="F3" s="11" t="inlineStr">
         <is>
-          <t>15 套</t>
+          <t>14 套</t>
         </is>
       </c>
     </row>
@@ -2215,15 +2013,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
-        <is>
-          <t>Altus Link 洋房6
-4016呎 (4+房)
-(23年-04月-27日)
-$4.10亿
-$102,000/呎</t>
-        </is>
-      </c>
+      <c r="F6" s="17" t="inlineStr"/>
       <c r="G6" s="16" t="inlineStr">
         <is>
           <t>Altus Link 洋房7
@@ -2249,7 +2039,7 @@
           <t>Bliss Link</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>Bliss Link 洋房1
 3723呎 (4+房)
@@ -2258,16 +2048,8 @@
 $103,895/呎</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>Bliss Link 洋房2
-3695呎 (4+房)
-(21年-11月-15日)
-$3.52亿
-$95,399/呎</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr"/>
+      <c r="D7" s="19" t="inlineStr">
         <is>
           <t>Bliss Link 洋房3
 3688呎 (4+房)
@@ -2276,7 +2058,7 @@
 -</t>
         </is>
       </c>
-      <c r="E7" s="19" t="inlineStr"/>
+      <c r="E7" s="17" t="inlineStr"/>
       <c r="F7" s="16" t="inlineStr">
         <is>
           <t>Bliss Link 洋房6
@@ -2295,15 +2077,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="H7" s="16" t="inlineStr">
-        <is>
-          <t>Bliss Link 洋房8
-3714呎 (4+房)
-(待售)
-暂无价格
-暂无呎价</t>
-        </is>
-      </c>
+      <c r="H7" s="17" t="inlineStr"/>
     </row>
     <row r="8" ht="80" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -2338,7 +2112,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="E8" s="19" t="inlineStr"/>
+      <c r="E8" s="17" t="inlineStr"/>
       <c r="F8" s="16" t="inlineStr">
         <is>
           <t>Colmo Link 洋房6

--- a/web/files/港岛-半山区东部-Central Peak II.xlsx
+++ b/web/files/港岛-半山区东部-Central Peak II.xlsx
@@ -242,13 +242,13 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -997,7 +997,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Altus Link 洋房7</t>
+          <t>Altus Link 洋房6</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1016,27 +1016,23 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>3671</v>
+        <v>4016</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2023-04-27</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>409632000</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>102000</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -1067,7 +1063,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Altus Link 洋房8</t>
+          <t>Altus Link 洋房7</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1086,7 +1082,7 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>3954</v>
+        <v>3671</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -1137,7 +1133,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Bliss Link 洋房1</t>
+          <t>Altus Link 洋房8</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -1156,23 +1152,27 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>3723</v>
+        <v>3954</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2022-01-10</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="n">
-        <v>386800000</v>
-      </c>
-      <c r="I9" s="5" t="n">
-        <v>103895</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Bliss Link 洋房3</t>
+          <t>Bliss Link 洋房1</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1222,27 +1222,23 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>3688</v>
+        <v>3723</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2022-01-10</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>386800000</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>103895</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -1251,12 +1247,12 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -1266,14 +1262,14 @@
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Bliss Link 洋房6</t>
+          <t>Bliss Link 洋房2</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -1292,27 +1288,23 @@
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>3691</v>
+        <v>3695</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2021-11-15</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>352500000</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>95399</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -1343,7 +1335,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Bliss Link 洋房7</t>
+          <t>Bliss Link 洋房3</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1362,11 +1354,11 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>3686</v>
+        <v>3688</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -1376,12 +1368,12 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1391,12 +1383,12 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -1406,14 +1398,14 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Colmo Link 洋房1</t>
+          <t>Bliss Link 洋房6</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -1428,11 +1420,11 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2776</v>
+        <v>3691</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -1483,7 +1475,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Colmo Link 洋房2</t>
+          <t>Bliss Link 洋房7</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1498,11 +1490,11 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>2754</v>
+        <v>3686</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -1553,7 +1545,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Colmo Link 洋房3</t>
+          <t>Bliss Link 洋房8</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -1568,11 +1560,11 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2754</v>
+        <v>3714</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -1623,7 +1615,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Colmo Link 洋房6</t>
+          <t>Colmo Link 洋房1</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1642,7 +1634,7 @@
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>2754</v>
+        <v>2776</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -1693,7 +1685,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Colmo Link 洋房7</t>
+          <t>Colmo Link 洋房2</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -1763,68 +1755,278 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
+          <t>Colmo Link 洋房3</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>2754</v>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Colmo Link 洋房6</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>2754</v>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Colmo Link 洋房7</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>2754</v>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
           <t>Colmo Link 洋房8</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>3房</t>
         </is>
       </c>
-      <c r="E18" s="4" t="n">
+      <c r="E21" s="4" t="n">
         <v>2780</v>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>待售</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M18" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N18" s="3" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -1900,7 +2102,7 @@
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>16 套</t>
+          <t>19 套</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
@@ -1915,7 +2117,7 @@
       </c>
       <c r="D3" s="14" t="inlineStr">
         <is>
-          <t>1 套</t>
+          <t>3 套</t>
         </is>
       </c>
       <c r="E3" s="15" t="inlineStr">
@@ -1925,7 +2127,7 @@
       </c>
       <c r="F3" s="11" t="inlineStr">
         <is>
-          <t>14 套</t>
+          <t>15 套</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2215,15 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr"/>
+      <c r="F6" s="17" t="inlineStr">
+        <is>
+          <t>Altus Link 洋房6
+4016呎 (4+房)
+(23年-04月-27日)
+$4.10亿
+$102,000/呎</t>
+        </is>
+      </c>
       <c r="G6" s="16" t="inlineStr">
         <is>
           <t>Altus Link 洋房7
@@ -2039,7 +2249,7 @@
           <t>Bliss Link</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>Bliss Link 洋房1
 3723呎 (4+房)
@@ -2048,8 +2258,16 @@
 $103,895/呎</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr"/>
-      <c r="D7" s="19" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>Bliss Link 洋房2
+3695呎 (4+房)
+(21年-11月-15日)
+$3.52亿
+$95,399/呎</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="inlineStr">
         <is>
           <t>Bliss Link 洋房3
 3688呎 (4+房)
@@ -2058,7 +2276,7 @@
 -</t>
         </is>
       </c>
-      <c r="E7" s="17" t="inlineStr"/>
+      <c r="E7" s="19" t="inlineStr"/>
       <c r="F7" s="16" t="inlineStr">
         <is>
           <t>Bliss Link 洋房6
@@ -2077,7 +2295,15 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr"/>
+      <c r="H7" s="16" t="inlineStr">
+        <is>
+          <t>Bliss Link 洋房8
+3714呎 (4+房)
+(待售)
+暂无价格
+暂无呎价</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="80" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -2112,7 +2338,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="E8" s="17" t="inlineStr"/>
+      <c r="E8" s="19" t="inlineStr"/>
       <c r="F8" s="16" t="inlineStr">
         <is>
           <t>Colmo Link 洋房6
